--- a/research/traditional_assets/database/data/canada/canada_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_banks_regional.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.1031</v>
+        <v>0.10255</v>
       </c>
       <c r="E2">
-        <v>0.175</v>
+        <v>0.05575000000000001</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>306</v>
+        <v>263.6</v>
       </c>
       <c r="L2">
-        <v>0.3614457831325301</v>
+        <v>0.3248305606900802</v>
       </c>
       <c r="M2">
-        <v>85.602</v>
+        <v>88.3655</v>
       </c>
       <c r="N2">
-        <v>0.02958015135284564</v>
+        <v>0.04673445102602072</v>
       </c>
       <c r="O2">
-        <v>0.2797450980392157</v>
+        <v>0.3352257207890743</v>
       </c>
       <c r="P2">
-        <v>85.602</v>
+        <v>86.94550000000001</v>
       </c>
       <c r="Q2">
-        <v>0.02958015135284564</v>
+        <v>0.04598344616035541</v>
       </c>
       <c r="R2">
-        <v>0.2797450980392157</v>
+        <v>0.3298387708649469</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.01606961993085537</v>
       </c>
       <c r="U2">
-        <v>305.4</v>
+        <v>130.4</v>
       </c>
       <c r="V2">
-        <v>0.1055323266180587</v>
+        <v>0.06896551724137931</v>
       </c>
       <c r="W2">
-        <v>0.1184160651372757</v>
+        <v>0.07761011705367697</v>
       </c>
       <c r="X2">
-        <v>0.05388782058101931</v>
+        <v>0.07712950250722156</v>
       </c>
       <c r="Y2">
-        <v>0.06452824455625641</v>
+        <v>0.0004806145464554129</v>
       </c>
       <c r="Z2">
-        <v>0.1981741573033708</v>
+        <v>0.1528864740215454</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04004527248072144</v>
+        <v>0.05704311759696973</v>
       </c>
       <c r="AC2">
-        <v>-0.04004527248072144</v>
+        <v>-0.05704311759696973</v>
       </c>
       <c r="AD2">
-        <v>2611.7</v>
+        <v>2977.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2611.7</v>
+        <v>2977.1</v>
       </c>
       <c r="AG2">
-        <v>2306.3</v>
+        <v>2846.7</v>
       </c>
       <c r="AH2">
-        <v>0.4743715489683231</v>
+        <v>0.6115778877955587</v>
       </c>
       <c r="AI2">
-        <v>0.4558020209776785</v>
+        <v>0.4985431040257217</v>
       </c>
       <c r="AJ2">
-        <v>0.4435021729933464</v>
+        <v>0.60088654353562</v>
       </c>
       <c r="AK2">
-        <v>0.4251636095492672</v>
+        <v>0.4873484900362939</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.113</v>
+        <v>0.08810000000000001</v>
       </c>
       <c r="E3">
-        <v>0.136</v>
+        <v>0.08070000000000001</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>287.9</v>
+        <v>247</v>
       </c>
       <c r="L3">
-        <v>0.360912623793406</v>
+        <v>0.3269358041032429</v>
       </c>
       <c r="M3">
-        <v>83.77200000000001</v>
+        <v>84.9355</v>
       </c>
       <c r="N3">
-        <v>0.03263038990378998</v>
+        <v>0.05033513097072419</v>
       </c>
       <c r="O3">
-        <v>0.2909760333449115</v>
+        <v>0.3438684210526316</v>
       </c>
       <c r="P3">
-        <v>83.77200000000001</v>
+        <v>84.9355</v>
       </c>
       <c r="Q3">
-        <v>0.03263038990378998</v>
+        <v>0.05033513097072419</v>
       </c>
       <c r="R3">
-        <v>0.2909760333449115</v>
+        <v>0.3438684210526316</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>86.40000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="V3">
-        <v>0.03365403342032486</v>
+        <v>0.03875785231717435</v>
       </c>
       <c r="W3">
-        <v>0.1302361349859767</v>
+        <v>0.09325681492109039</v>
       </c>
       <c r="X3">
-        <v>0.06112327857371852</v>
+        <v>0.08773915646262115</v>
       </c>
       <c r="Y3">
-        <v>0.06911285641225814</v>
+        <v>0.005517658458469243</v>
       </c>
       <c r="Z3">
-        <v>0.1872007885102788</v>
+        <v>0.1457762513024351</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.03929915035718578</v>
+        <v>0.05471251447658899</v>
       </c>
       <c r="AC3">
-        <v>-0.03929915035718578</v>
+        <v>-0.05471251447658899</v>
       </c>
       <c r="AD3">
-        <v>2530.7</v>
+        <v>2896.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2530.7</v>
+        <v>2896.9</v>
       </c>
       <c r="AG3">
-        <v>2444.3</v>
+        <v>2831.5</v>
       </c>
       <c r="AH3">
-        <v>0.4964103570027462</v>
+        <v>0.631917631917632</v>
       </c>
       <c r="AI3">
-        <v>0.4703029176732949</v>
+        <v>0.514154375876329</v>
       </c>
       <c r="AJ3">
-        <v>0.4877284699497166</v>
+        <v>0.6265905419460489</v>
       </c>
       <c r="AK3">
-        <v>0.4616590488422165</v>
+        <v>0.5084487062076891</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -823,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VersaBank (TSX:VB)</t>
+          <t>VersaBank (TSX:VBNK)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.09320000000000001</v>
+        <v>0.117</v>
       </c>
       <c r="E4">
-        <v>0.214</v>
+        <v>0.0308</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,85 +850,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>18.1</v>
+        <v>16.6</v>
       </c>
       <c r="L4">
-        <v>0.3701431492842536</v>
+        <v>0.2964285714285714</v>
       </c>
       <c r="M4">
-        <v>1.83</v>
+        <v>3.43</v>
       </c>
       <c r="N4">
-        <v>0.005603184323331292</v>
+        <v>0.01686332350049164</v>
       </c>
       <c r="O4">
-        <v>0.1011049723756906</v>
+        <v>0.2066265060240964</v>
       </c>
       <c r="P4">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="Q4">
-        <v>0.005603184323331292</v>
+        <v>0.009882005899705013</v>
       </c>
       <c r="R4">
-        <v>0.1011049723756906</v>
+        <v>0.1210843373493976</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.41399416909621</v>
       </c>
       <c r="U4">
-        <v>219</v>
+        <v>65</v>
       </c>
       <c r="V4">
-        <v>0.670545009185548</v>
+        <v>0.319567354965585</v>
       </c>
       <c r="W4">
-        <v>0.1065959952885748</v>
+        <v>0.06196341918626355</v>
       </c>
       <c r="X4">
-        <v>0.0466523625883201</v>
+        <v>0.06651984855182198</v>
       </c>
       <c r="Y4">
-        <v>0.0599436327002547</v>
+        <v>-0.004556429365558438</v>
       </c>
       <c r="Z4">
-        <v>4.527777777777773</v>
+        <v>0.4470700942040556</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04079139460425711</v>
+        <v>0.05937372071735046</v>
       </c>
       <c r="AC4">
-        <v>-0.04079139460425711</v>
+        <v>-0.05937372071735046</v>
       </c>
       <c r="AD4">
-        <v>81</v>
+        <v>80.2</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>81</v>
+        <v>80.2</v>
       </c>
       <c r="AG4">
-        <v>-138</v>
+        <v>15.2</v>
       </c>
       <c r="AH4">
-        <v>0.1987242394504416</v>
+        <v>0.2827926657263752</v>
       </c>
       <c r="AI4">
-        <v>0.2321582115219261</v>
+        <v>0.2377705306848503</v>
       </c>
       <c r="AJ4">
-        <v>-0.7317073170731706</v>
+        <v>0.06953339432753888</v>
       </c>
       <c r="AK4">
-        <v>-1.062355658198614</v>
+        <v>0.05582078589790673</v>
       </c>
       <c r="AL4">
         <v>0</v>

--- a/research/traditional_assets/database/data/canada/canada_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_banks_regional.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.10255</v>
+        <v>0.11825</v>
       </c>
       <c r="E2">
-        <v>0.05575000000000001</v>
+        <v>0.1219</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>263.6</v>
+        <v>604</v>
       </c>
       <c r="L2">
-        <v>0.3248305606900802</v>
+        <v>0.3618716673656462</v>
       </c>
       <c r="M2">
-        <v>88.3655</v>
+        <v>137.25</v>
       </c>
       <c r="N2">
-        <v>0.04673445102602072</v>
+        <v>0.02718521599619704</v>
       </c>
       <c r="O2">
-        <v>0.3352257207890743</v>
+        <v>0.2272350993377484</v>
       </c>
       <c r="P2">
-        <v>86.94550000000001</v>
+        <v>127.68</v>
       </c>
       <c r="Q2">
-        <v>0.04598344616035541</v>
+        <v>0.02528967853110702</v>
       </c>
       <c r="R2">
-        <v>0.3298387708649469</v>
+        <v>0.2113907284768212</v>
       </c>
       <c r="S2">
-        <v>1.42</v>
+        <v>9.57</v>
       </c>
       <c r="T2">
-        <v>0.01606961993085537</v>
+        <v>0.06972677595628415</v>
       </c>
       <c r="U2">
-        <v>130.4</v>
+        <v>538.7</v>
       </c>
       <c r="V2">
-        <v>0.06896551724137931</v>
+        <v>0.1067007348426328</v>
       </c>
       <c r="W2">
-        <v>0.07761011705367697</v>
+        <v>0.1182419292104239</v>
       </c>
       <c r="X2">
-        <v>0.07712950250722156</v>
+        <v>0.06538674072254053</v>
       </c>
       <c r="Y2">
-        <v>0.0004806145464554129</v>
+        <v>0.05285518848788341</v>
       </c>
       <c r="Z2">
-        <v>0.1528864740215454</v>
+        <v>0.09905826104709405</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05704311759696973</v>
+        <v>0.04810792385032006</v>
       </c>
       <c r="AC2">
-        <v>-0.05704311759696973</v>
+        <v>-0.04810792385032006</v>
       </c>
       <c r="AD2">
-        <v>2977.1</v>
+        <v>15569.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2977.1</v>
+        <v>15569.1</v>
       </c>
       <c r="AG2">
-        <v>2846.7</v>
+        <v>15030.4</v>
       </c>
       <c r="AH2">
-        <v>0.6115778877955587</v>
+        <v>0.7551290632366209</v>
       </c>
       <c r="AI2">
-        <v>0.4985431040257217</v>
+        <v>0.7489212889694882</v>
       </c>
       <c r="AJ2">
-        <v>0.60088654353562</v>
+        <v>0.74855944738559</v>
       </c>
       <c r="AK2">
-        <v>0.4873484900362939</v>
+        <v>0.742241975308642</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.08810000000000001</v>
+        <v>0.0765</v>
       </c>
       <c r="E3">
-        <v>0.08070000000000001</v>
+        <v>0.0588</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>247</v>
+        <v>252.5</v>
       </c>
       <c r="L3">
-        <v>0.3269358041032429</v>
+        <v>0.3229313211408109</v>
       </c>
       <c r="M3">
-        <v>84.9355</v>
+        <v>90</v>
       </c>
       <c r="N3">
-        <v>0.05033513097072419</v>
+        <v>0.03992547245142401</v>
       </c>
       <c r="O3">
-        <v>0.3438684210526316</v>
+        <v>0.3564356435643564</v>
       </c>
       <c r="P3">
-        <v>84.9355</v>
+        <v>90</v>
       </c>
       <c r="Q3">
-        <v>0.05033513097072419</v>
+        <v>0.03992547245142401</v>
       </c>
       <c r="R3">
-        <v>0.3438684210526316</v>
+        <v>0.3564356435643564</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>65.40000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="V3">
-        <v>0.03875785231717435</v>
+        <v>0.021249223671369</v>
       </c>
       <c r="W3">
-        <v>0.09325681492109039</v>
+        <v>0.09886065541678087</v>
       </c>
       <c r="X3">
-        <v>0.08773915646262115</v>
+        <v>0.06538674072254053</v>
       </c>
       <c r="Y3">
-        <v>0.005517658458469243</v>
+        <v>0.03347391469424034</v>
       </c>
       <c r="Z3">
-        <v>0.1457762513024351</v>
+        <v>0.1427971363868799</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05471251447658899</v>
+        <v>0.04698342517387548</v>
       </c>
       <c r="AC3">
-        <v>-0.05471251447658899</v>
+        <v>-0.04698342517387548</v>
       </c>
       <c r="AD3">
-        <v>2896.9</v>
+        <v>2989.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2896.9</v>
+        <v>2989.5</v>
       </c>
       <c r="AG3">
-        <v>2831.5</v>
+        <v>2941.6</v>
       </c>
       <c r="AH3">
-        <v>0.631917631917632</v>
+        <v>0.5701127066765833</v>
       </c>
       <c r="AI3">
-        <v>0.514154375876329</v>
+        <v>0.5076672270620001</v>
       </c>
       <c r="AJ3">
-        <v>0.6265905419460489</v>
+        <v>0.566149582354979</v>
       </c>
       <c r="AK3">
-        <v>0.5084487062076891</v>
+        <v>0.5036296397753733</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -823,117 +823,233 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>EQB Inc. (TSX:EQB)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>321.1</v>
+      </c>
+      <c r="L4">
+        <v>0.3967136150234742</v>
+      </c>
+      <c r="M4">
+        <v>35.8</v>
+      </c>
+      <c r="N4">
+        <v>0.01427090807621781</v>
+      </c>
+      <c r="O4">
+        <v>0.1114917471192775</v>
+      </c>
+      <c r="P4">
+        <v>35.8</v>
+      </c>
+      <c r="Q4">
+        <v>0.01427090807621781</v>
+      </c>
+      <c r="R4">
+        <v>0.1114917471192775</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>395.6</v>
+      </c>
+      <c r="V4">
+        <v>0.157697520529379</v>
+      </c>
+      <c r="W4">
+        <v>0.2108061974789916</v>
+      </c>
+      <c r="X4">
+        <v>0.1015715033883097</v>
+      </c>
+      <c r="Y4">
+        <v>0.1092346940906819</v>
+      </c>
+      <c r="Z4">
+        <v>0.07287952458130739</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.04810792385032006</v>
+      </c>
+      <c r="AC4">
+        <v>-0.04810792385032006</v>
+      </c>
+      <c r="AD4">
+        <v>12500</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>12500</v>
+      </c>
+      <c r="AG4">
+        <v>12104.4</v>
+      </c>
+      <c r="AH4">
+        <v>0.8328558293245206</v>
+      </c>
+      <c r="AI4">
+        <v>0.8591773892004839</v>
+      </c>
+      <c r="AJ4">
+        <v>0.8283309382057072</v>
+      </c>
+      <c r="AK4">
+        <v>0.8552412175338439</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>VersaBank (TSX:VBNK)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Banks (Regional)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.117</v>
-      </c>
-      <c r="E4">
-        <v>0.0308</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>16.6</v>
-      </c>
-      <c r="L4">
-        <v>0.2964285714285714</v>
-      </c>
-      <c r="M4">
-        <v>3.43</v>
-      </c>
-      <c r="N4">
-        <v>0.01686332350049164</v>
-      </c>
-      <c r="O4">
-        <v>0.2066265060240964</v>
-      </c>
-      <c r="P4">
-        <v>2.01</v>
-      </c>
-      <c r="Q4">
-        <v>0.009882005899705013</v>
-      </c>
-      <c r="R4">
-        <v>0.1210843373493976</v>
-      </c>
-      <c r="S4">
-        <v>1.42</v>
-      </c>
-      <c r="T4">
-        <v>0.41399416909621</v>
-      </c>
-      <c r="U4">
-        <v>65</v>
-      </c>
-      <c r="V4">
-        <v>0.319567354965585</v>
-      </c>
-      <c r="W4">
-        <v>0.06196341918626355</v>
-      </c>
-      <c r="X4">
-        <v>0.06651984855182198</v>
-      </c>
-      <c r="Y4">
-        <v>-0.004556429365558438</v>
-      </c>
-      <c r="Z4">
-        <v>0.4470700942040556</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.05937372071735046</v>
-      </c>
-      <c r="AC4">
-        <v>-0.05937372071735046</v>
-      </c>
-      <c r="AD4">
-        <v>80.2</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>80.2</v>
-      </c>
-      <c r="AG4">
-        <v>15.2</v>
-      </c>
-      <c r="AH4">
-        <v>0.2827926657263752</v>
-      </c>
-      <c r="AI4">
-        <v>0.2377705306848503</v>
-      </c>
-      <c r="AJ4">
-        <v>0.06953339432753888</v>
-      </c>
-      <c r="AK4">
-        <v>0.05582078589790673</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
+      <c r="D5">
+        <v>0.16</v>
+      </c>
+      <c r="E5">
+        <v>0.185</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>30.4</v>
+      </c>
+      <c r="L5">
+        <v>0.390745501285347</v>
+      </c>
+      <c r="M5">
+        <v>11.45</v>
+      </c>
+      <c r="N5">
+        <v>0.04004896817068905</v>
+      </c>
+      <c r="O5">
+        <v>0.3766447368421053</v>
+      </c>
+      <c r="P5">
+        <v>1.88</v>
+      </c>
+      <c r="Q5">
+        <v>0.006575725778244141</v>
+      </c>
+      <c r="R5">
+        <v>0.06184210526315789</v>
+      </c>
+      <c r="S5">
+        <v>9.57</v>
+      </c>
+      <c r="T5">
+        <v>0.8358078602620088</v>
+      </c>
+      <c r="U5">
+        <v>95.2</v>
+      </c>
+      <c r="V5">
+        <v>0.3329835606855544</v>
+      </c>
+      <c r="W5">
+        <v>0.1182419292104239</v>
+      </c>
+      <c r="X5">
+        <v>0.05501845308289093</v>
+      </c>
+      <c r="Y5">
+        <v>0.06322347612753301</v>
+      </c>
+      <c r="Z5">
+        <v>0.2902118770516264</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.0511767397165486</v>
+      </c>
+      <c r="AC5">
+        <v>-0.0511767397165486</v>
+      </c>
+      <c r="AD5">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="AG5">
+        <v>-15.60000000000001</v>
+      </c>
+      <c r="AH5">
+        <v>0.2177838577291382</v>
+      </c>
+      <c r="AI5">
+        <v>0.2266514806378132</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.05771365149833523</v>
+      </c>
+      <c r="AK5">
+        <v>-0.06093750000000003</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
         <v>0</v>
       </c>
     </row>
